--- a/data/raw/spot_prices/Precio_Bolsa_Nacional_($kwh)_2025.xlsx
+++ b/data/raw/spot_prices/Precio_Bolsa_Nacional_($kwh)_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Dev\maestria-trabajo-integrador\data\raw\spot_prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817AE2A3-A937-4D2E-A510-55662094E1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECC8A28-AD78-415E-87E4-008A8899049B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="29">
   <si>
     <t>Fecha</t>
   </si>
@@ -199,7 +199,67 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC8DAB9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -560,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z182"/>
+  <dimension ref="A1:Z213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -15127,18 +15187,2513 @@
         <v>28</v>
       </c>
     </row>
+    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A183" s="3">
+        <v>45839</v>
+      </c>
+      <c r="B183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="C183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="D183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="E183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="F183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="G183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="H183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="I183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="J183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="K183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="L183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="M183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="N183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="O183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="P183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="Q183" s="1">
+        <v>106.03</v>
+      </c>
+      <c r="R183" s="1">
+        <v>106.03</v>
+      </c>
+      <c r="S183" s="1">
+        <v>106.03</v>
+      </c>
+      <c r="T183" s="1">
+        <v>111.51</v>
+      </c>
+      <c r="U183" s="1">
+        <v>113.03</v>
+      </c>
+      <c r="V183" s="1">
+        <v>111.51</v>
+      </c>
+      <c r="W183" s="1">
+        <v>111.51</v>
+      </c>
+      <c r="X183" s="1">
+        <v>106.03</v>
+      </c>
+      <c r="Y183" s="1">
+        <v>104.51</v>
+      </c>
+      <c r="Z183" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A184" s="3">
+        <v>45840</v>
+      </c>
+      <c r="B184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="C184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="D184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="E184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="F184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="G184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="H184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="I184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="J184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="K184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="L184" s="1">
+        <v>108.23</v>
+      </c>
+      <c r="M184" s="1">
+        <v>109.36</v>
+      </c>
+      <c r="N184" s="1">
+        <v>109.36</v>
+      </c>
+      <c r="O184" s="1">
+        <v>109.36</v>
+      </c>
+      <c r="P184" s="1">
+        <v>114.87</v>
+      </c>
+      <c r="Q184" s="1">
+        <v>115.23</v>
+      </c>
+      <c r="R184" s="1">
+        <v>115.23</v>
+      </c>
+      <c r="S184" s="1">
+        <v>115.23</v>
+      </c>
+      <c r="T184" s="1">
+        <v>115.23</v>
+      </c>
+      <c r="U184" s="1">
+        <v>461.76</v>
+      </c>
+      <c r="V184" s="1">
+        <v>191.76</v>
+      </c>
+      <c r="W184" s="1">
+        <v>115.23</v>
+      </c>
+      <c r="X184" s="1">
+        <v>114.87</v>
+      </c>
+      <c r="Y184" s="1">
+        <v>109.36</v>
+      </c>
+      <c r="Z184" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A185" s="3">
+        <v>45841</v>
+      </c>
+      <c r="B185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="C185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="D185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="E185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="F185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="G185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="H185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="I185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="J185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="K185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="L185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="M185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="N185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="O185" s="1">
+        <v>110.15</v>
+      </c>
+      <c r="P185" s="1">
+        <v>116.02</v>
+      </c>
+      <c r="Q185" s="1">
+        <v>116.02</v>
+      </c>
+      <c r="R185" s="1">
+        <v>116.05</v>
+      </c>
+      <c r="S185" s="1">
+        <v>116.02</v>
+      </c>
+      <c r="T185" s="1">
+        <v>117.55</v>
+      </c>
+      <c r="U185" s="1">
+        <v>192.55</v>
+      </c>
+      <c r="V185" s="1">
+        <v>117.55</v>
+      </c>
+      <c r="W185" s="1">
+        <v>117.55</v>
+      </c>
+      <c r="X185" s="1">
+        <v>116.02</v>
+      </c>
+      <c r="Y185" s="1">
+        <v>109.02</v>
+      </c>
+      <c r="Z185" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A186" s="3">
+        <v>45842</v>
+      </c>
+      <c r="B186" s="1">
+        <v>107.21</v>
+      </c>
+      <c r="C186" s="1">
+        <v>107.21</v>
+      </c>
+      <c r="D186" s="1">
+        <v>107.21</v>
+      </c>
+      <c r="E186" s="1">
+        <v>107.21</v>
+      </c>
+      <c r="F186" s="1">
+        <v>107.21</v>
+      </c>
+      <c r="G186" s="1">
+        <v>107.21</v>
+      </c>
+      <c r="H186" s="1">
+        <v>107.54</v>
+      </c>
+      <c r="I186" s="1">
+        <v>107.54</v>
+      </c>
+      <c r="J186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="K186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="L186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="M186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="N186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="O186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="P186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="Q186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="R186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="S186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="T186" s="1">
+        <v>114.21</v>
+      </c>
+      <c r="U186" s="1">
+        <v>190.74</v>
+      </c>
+      <c r="V186" s="1">
+        <v>114.21</v>
+      </c>
+      <c r="W186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="X186" s="1">
+        <v>113.85</v>
+      </c>
+      <c r="Y186" s="1">
+        <v>107.54</v>
+      </c>
+      <c r="Z186" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A187" s="3">
+        <v>45843</v>
+      </c>
+      <c r="B187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="C187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="D187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="E187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="F187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="G187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="H187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="I187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="J187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="K187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="L187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="M187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="N187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="O187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="P187" s="1">
+        <v>105.76</v>
+      </c>
+      <c r="Q187" s="1">
+        <v>106.09</v>
+      </c>
+      <c r="R187" s="1">
+        <v>112.4</v>
+      </c>
+      <c r="S187" s="1">
+        <v>112.4</v>
+      </c>
+      <c r="T187" s="1">
+        <v>112.76</v>
+      </c>
+      <c r="U187" s="1">
+        <v>149.29</v>
+      </c>
+      <c r="V187" s="1">
+        <v>112.76</v>
+      </c>
+      <c r="W187" s="1">
+        <v>112.76</v>
+      </c>
+      <c r="X187" s="1">
+        <v>112.4</v>
+      </c>
+      <c r="Y187" s="1">
+        <v>106.09</v>
+      </c>
+      <c r="Z187" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A188" s="3">
+        <v>45844</v>
+      </c>
+      <c r="B188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="C188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="D188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="E188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="F188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="G188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="H188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="I188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="J188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="K188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="L188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="M188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="N188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="O188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="P188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="Q188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="R188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="S188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="T188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="U188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="V188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="W188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="X188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="Y188" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="Z188" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A189" s="3">
+        <v>45845</v>
+      </c>
+      <c r="B189" s="1">
+        <v>105.64</v>
+      </c>
+      <c r="C189" s="1">
+        <v>105.64</v>
+      </c>
+      <c r="D189" s="1">
+        <v>105.64</v>
+      </c>
+      <c r="E189" s="1">
+        <v>105.64</v>
+      </c>
+      <c r="F189" s="1">
+        <v>105.64</v>
+      </c>
+      <c r="G189" s="1">
+        <v>105.64</v>
+      </c>
+      <c r="H189" s="1">
+        <v>105.64</v>
+      </c>
+      <c r="I189" s="1">
+        <v>105.64</v>
+      </c>
+      <c r="J189" s="1">
+        <v>105.65</v>
+      </c>
+      <c r="K189" s="1">
+        <v>105.65</v>
+      </c>
+      <c r="L189" s="1">
+        <v>105.65</v>
+      </c>
+      <c r="M189" s="1">
+        <v>112.28</v>
+      </c>
+      <c r="N189" s="1">
+        <v>112.67</v>
+      </c>
+      <c r="O189" s="1">
+        <v>112.28</v>
+      </c>
+      <c r="P189" s="1">
+        <v>113.14</v>
+      </c>
+      <c r="Q189" s="1">
+        <v>149.16999999999999</v>
+      </c>
+      <c r="R189" s="1">
+        <v>149.16999999999999</v>
+      </c>
+      <c r="S189" s="1">
+        <v>149.16999999999999</v>
+      </c>
+      <c r="T189" s="1">
+        <v>149.16999999999999</v>
+      </c>
+      <c r="U189" s="1">
+        <v>439.17</v>
+      </c>
+      <c r="V189" s="1">
+        <v>149.16999999999999</v>
+      </c>
+      <c r="W189" s="1">
+        <v>149.16999999999999</v>
+      </c>
+      <c r="X189" s="1">
+        <v>113.14</v>
+      </c>
+      <c r="Y189" s="1">
+        <v>112.28</v>
+      </c>
+      <c r="Z189" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A190" s="3">
+        <v>45846</v>
+      </c>
+      <c r="B190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="C190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="D190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="E190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="F190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="G190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="H190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="I190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="J190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="K190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="L190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="M190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="N190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="O190" s="1">
+        <v>114.73</v>
+      </c>
+      <c r="P190" s="1">
+        <v>115.59</v>
+      </c>
+      <c r="Q190" s="1">
+        <v>151.62</v>
+      </c>
+      <c r="R190" s="1">
+        <v>151.62</v>
+      </c>
+      <c r="S190" s="1">
+        <v>151.62</v>
+      </c>
+      <c r="T190" s="1">
+        <v>191.62</v>
+      </c>
+      <c r="U190" s="1">
+        <v>833.58</v>
+      </c>
+      <c r="V190" s="1">
+        <v>151.62</v>
+      </c>
+      <c r="W190" s="1">
+        <v>151.62</v>
+      </c>
+      <c r="X190" s="1">
+        <v>115.59</v>
+      </c>
+      <c r="Y190" s="1">
+        <v>108.1</v>
+      </c>
+      <c r="Z190" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A191" s="3">
+        <v>45847</v>
+      </c>
+      <c r="B191" s="1">
+        <v>112.19</v>
+      </c>
+      <c r="C191" s="1">
+        <v>112.19</v>
+      </c>
+      <c r="D191" s="1">
+        <v>112.19</v>
+      </c>
+      <c r="E191" s="1">
+        <v>112.19</v>
+      </c>
+      <c r="F191" s="1">
+        <v>112.19</v>
+      </c>
+      <c r="G191" s="1">
+        <v>112.19</v>
+      </c>
+      <c r="H191" s="1">
+        <v>112.19</v>
+      </c>
+      <c r="I191" s="1">
+        <v>112.19</v>
+      </c>
+      <c r="J191" s="1">
+        <v>119.62</v>
+      </c>
+      <c r="K191" s="1">
+        <v>118.83</v>
+      </c>
+      <c r="L191" s="1">
+        <v>118.83</v>
+      </c>
+      <c r="M191" s="1">
+        <v>119.68</v>
+      </c>
+      <c r="N191" s="1">
+        <v>119.68</v>
+      </c>
+      <c r="O191" s="1">
+        <v>119.68</v>
+      </c>
+      <c r="P191" s="1">
+        <v>195.72</v>
+      </c>
+      <c r="Q191" s="1">
+        <v>225.72</v>
+      </c>
+      <c r="R191" s="1">
+        <v>225.72</v>
+      </c>
+      <c r="S191" s="1">
+        <v>225.72</v>
+      </c>
+      <c r="T191" s="1">
+        <v>302.72000000000003</v>
+      </c>
+      <c r="U191" s="1">
+        <v>837.68</v>
+      </c>
+      <c r="V191" s="1">
+        <v>225.72</v>
+      </c>
+      <c r="W191" s="1">
+        <v>195.72</v>
+      </c>
+      <c r="X191" s="1">
+        <v>195.72</v>
+      </c>
+      <c r="Y191" s="1">
+        <v>119.68</v>
+      </c>
+      <c r="Z191" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A192" s="3">
+        <v>45848</v>
+      </c>
+      <c r="B192" s="1">
+        <v>115.25</v>
+      </c>
+      <c r="C192" s="1">
+        <v>115.25</v>
+      </c>
+      <c r="D192" s="1">
+        <v>115.25</v>
+      </c>
+      <c r="E192" s="1">
+        <v>115.25</v>
+      </c>
+      <c r="F192" s="1">
+        <v>115.25</v>
+      </c>
+      <c r="G192" s="1">
+        <v>115.36</v>
+      </c>
+      <c r="H192" s="1">
+        <v>156.28</v>
+      </c>
+      <c r="I192" s="1">
+        <v>156.28</v>
+      </c>
+      <c r="J192" s="1">
+        <v>156.28</v>
+      </c>
+      <c r="K192" s="1">
+        <v>156.28</v>
+      </c>
+      <c r="L192" s="1">
+        <v>156.28</v>
+      </c>
+      <c r="M192" s="1">
+        <v>159.28</v>
+      </c>
+      <c r="N192" s="1">
+        <v>159.28</v>
+      </c>
+      <c r="O192" s="1">
+        <v>211.28</v>
+      </c>
+      <c r="P192" s="1">
+        <v>216.28</v>
+      </c>
+      <c r="Q192" s="1">
+        <v>216.28</v>
+      </c>
+      <c r="R192" s="1">
+        <v>216.28</v>
+      </c>
+      <c r="S192" s="1">
+        <v>216.28</v>
+      </c>
+      <c r="T192" s="1">
+        <v>216.28</v>
+      </c>
+      <c r="U192" s="1">
+        <v>221.28</v>
+      </c>
+      <c r="V192" s="1">
+        <v>221.28</v>
+      </c>
+      <c r="W192" s="1">
+        <v>216.28</v>
+      </c>
+      <c r="X192" s="1">
+        <v>159.28</v>
+      </c>
+      <c r="Y192" s="1">
+        <v>156.28</v>
+      </c>
+      <c r="Z192" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A193" s="3">
+        <v>45849</v>
+      </c>
+      <c r="B193" s="1">
+        <v>112.01</v>
+      </c>
+      <c r="C193" s="1">
+        <v>105.37</v>
+      </c>
+      <c r="D193" s="1">
+        <v>105.37</v>
+      </c>
+      <c r="E193" s="1">
+        <v>105.37</v>
+      </c>
+      <c r="F193" s="1">
+        <v>112.01</v>
+      </c>
+      <c r="G193" s="1">
+        <v>112.87</v>
+      </c>
+      <c r="H193" s="1">
+        <v>112.87</v>
+      </c>
+      <c r="I193" s="1">
+        <v>112.87</v>
+      </c>
+      <c r="J193" s="1">
+        <v>112.87</v>
+      </c>
+      <c r="K193" s="1">
+        <v>112.87</v>
+      </c>
+      <c r="L193" s="1">
+        <v>112.87</v>
+      </c>
+      <c r="M193" s="1">
+        <v>112.87</v>
+      </c>
+      <c r="N193" s="1">
+        <v>112.87</v>
+      </c>
+      <c r="O193" s="1">
+        <v>146.9</v>
+      </c>
+      <c r="P193" s="1">
+        <v>146.9</v>
+      </c>
+      <c r="Q193" s="1">
+        <v>146.9</v>
+      </c>
+      <c r="R193" s="1">
+        <v>189.9</v>
+      </c>
+      <c r="S193" s="1">
+        <v>189.9</v>
+      </c>
+      <c r="T193" s="1">
+        <v>198.9</v>
+      </c>
+      <c r="U193" s="1">
+        <v>198.9</v>
+      </c>
+      <c r="V193" s="1">
+        <v>198.9</v>
+      </c>
+      <c r="W193" s="1">
+        <v>198.9</v>
+      </c>
+      <c r="X193" s="1">
+        <v>189.9</v>
+      </c>
+      <c r="Y193" s="1">
+        <v>146.9</v>
+      </c>
+      <c r="Z193" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A194" s="3">
+        <v>45850</v>
+      </c>
+      <c r="B194" s="1">
+        <v>113.53</v>
+      </c>
+      <c r="C194" s="1">
+        <v>113.53</v>
+      </c>
+      <c r="D194" s="1">
+        <v>113.53</v>
+      </c>
+      <c r="E194" s="1">
+        <v>113.53</v>
+      </c>
+      <c r="F194" s="1">
+        <v>113.53</v>
+      </c>
+      <c r="G194" s="1">
+        <v>113.53</v>
+      </c>
+      <c r="H194" s="1">
+        <v>113.53</v>
+      </c>
+      <c r="I194" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="J194" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="K194" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="L194" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="M194" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="N194" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="O194" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="P194" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="Q194" s="1">
+        <v>114.29</v>
+      </c>
+      <c r="R194" s="1">
+        <v>144.57</v>
+      </c>
+      <c r="S194" s="1">
+        <v>144.57</v>
+      </c>
+      <c r="T194" s="1">
+        <v>144.57</v>
+      </c>
+      <c r="U194" s="1">
+        <v>144.57</v>
+      </c>
+      <c r="V194" s="1">
+        <v>144.57</v>
+      </c>
+      <c r="W194" s="1">
+        <v>144.57</v>
+      </c>
+      <c r="X194" s="1">
+        <v>153.57</v>
+      </c>
+      <c r="Y194" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="Z194" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A195" s="3">
+        <v>45851</v>
+      </c>
+      <c r="B195" s="1">
+        <v>116.72</v>
+      </c>
+      <c r="C195" s="1">
+        <v>116.72</v>
+      </c>
+      <c r="D195" s="1">
+        <v>115.61</v>
+      </c>
+      <c r="E195" s="1">
+        <v>110.08</v>
+      </c>
+      <c r="F195" s="1">
+        <v>115.61</v>
+      </c>
+      <c r="G195" s="1">
+        <v>110.08</v>
+      </c>
+      <c r="H195" s="1">
+        <v>110.08</v>
+      </c>
+      <c r="I195" s="1">
+        <v>110.08</v>
+      </c>
+      <c r="J195" s="1">
+        <v>110.08</v>
+      </c>
+      <c r="K195" s="1">
+        <v>110.08</v>
+      </c>
+      <c r="L195" s="1">
+        <v>110.08</v>
+      </c>
+      <c r="M195" s="1">
+        <v>110.08</v>
+      </c>
+      <c r="N195" s="1">
+        <v>115.61</v>
+      </c>
+      <c r="O195" s="1">
+        <v>116.72</v>
+      </c>
+      <c r="P195" s="1">
+        <v>116.72</v>
+      </c>
+      <c r="Q195" s="1">
+        <v>116.72</v>
+      </c>
+      <c r="R195" s="1">
+        <v>116.72</v>
+      </c>
+      <c r="S195" s="1">
+        <v>117.58</v>
+      </c>
+      <c r="T195" s="1">
+        <v>142.61000000000001</v>
+      </c>
+      <c r="U195" s="1">
+        <v>148.61000000000001</v>
+      </c>
+      <c r="V195" s="1">
+        <v>148.61000000000001</v>
+      </c>
+      <c r="W195" s="1">
+        <v>142.61000000000001</v>
+      </c>
+      <c r="X195" s="1">
+        <v>117.61</v>
+      </c>
+      <c r="Y195" s="1">
+        <v>117.58</v>
+      </c>
+      <c r="Z195" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A196" s="3">
+        <v>45852</v>
+      </c>
+      <c r="B196" s="1">
+        <v>105.81</v>
+      </c>
+      <c r="C196" s="1">
+        <v>105.81</v>
+      </c>
+      <c r="D196" s="1">
+        <v>105.81</v>
+      </c>
+      <c r="E196" s="1">
+        <v>105.81</v>
+      </c>
+      <c r="F196" s="1">
+        <v>105.81</v>
+      </c>
+      <c r="G196" s="1">
+        <v>105.81</v>
+      </c>
+      <c r="H196" s="1">
+        <v>105.82</v>
+      </c>
+      <c r="I196" s="1">
+        <v>105.82</v>
+      </c>
+      <c r="J196" s="1">
+        <v>105.82</v>
+      </c>
+      <c r="K196" s="1">
+        <v>111.34</v>
+      </c>
+      <c r="L196" s="1">
+        <v>111.34</v>
+      </c>
+      <c r="M196" s="1">
+        <v>112.45</v>
+      </c>
+      <c r="N196" s="1">
+        <v>112.45</v>
+      </c>
+      <c r="O196" s="1">
+        <v>112.45</v>
+      </c>
+      <c r="P196" s="1">
+        <v>113.31</v>
+      </c>
+      <c r="Q196" s="1">
+        <v>113.34</v>
+      </c>
+      <c r="R196" s="1">
+        <v>113.34</v>
+      </c>
+      <c r="S196" s="1">
+        <v>113.34</v>
+      </c>
+      <c r="T196" s="1">
+        <v>113.34</v>
+      </c>
+      <c r="U196" s="1">
+        <v>113.52</v>
+      </c>
+      <c r="V196" s="1">
+        <v>113.34</v>
+      </c>
+      <c r="W196" s="1">
+        <v>113.34</v>
+      </c>
+      <c r="X196" s="1">
+        <v>113.31</v>
+      </c>
+      <c r="Y196" s="1">
+        <v>112.45</v>
+      </c>
+      <c r="Z196" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A197" s="3">
+        <v>45853</v>
+      </c>
+      <c r="B197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="C197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="D197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="E197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="F197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="G197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="H197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="I197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="J197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="K197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="L197" s="1">
+        <v>106.92</v>
+      </c>
+      <c r="M197" s="1">
+        <v>113.56</v>
+      </c>
+      <c r="N197" s="1">
+        <v>113.56</v>
+      </c>
+      <c r="O197" s="1">
+        <v>114.42</v>
+      </c>
+      <c r="P197" s="1">
+        <v>114.42</v>
+      </c>
+      <c r="Q197" s="1">
+        <v>130.44999999999999</v>
+      </c>
+      <c r="R197" s="1">
+        <v>130.44999999999999</v>
+      </c>
+      <c r="S197" s="1">
+        <v>130.44999999999999</v>
+      </c>
+      <c r="T197" s="1">
+        <v>192.45</v>
+      </c>
+      <c r="U197" s="1">
+        <v>360.45</v>
+      </c>
+      <c r="V197" s="1">
+        <v>192.45</v>
+      </c>
+      <c r="W197" s="1">
+        <v>130.44999999999999</v>
+      </c>
+      <c r="X197" s="1">
+        <v>130.44999999999999</v>
+      </c>
+      <c r="Y197" s="1">
+        <v>114.44</v>
+      </c>
+      <c r="Z197" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A198" s="3">
+        <v>45854</v>
+      </c>
+      <c r="B198" s="1">
+        <v>108.58</v>
+      </c>
+      <c r="C198" s="1">
+        <v>108.58</v>
+      </c>
+      <c r="D198" s="1">
+        <v>106.06</v>
+      </c>
+      <c r="E198" s="1">
+        <v>106.05</v>
+      </c>
+      <c r="F198" s="1">
+        <v>109.08</v>
+      </c>
+      <c r="G198" s="1">
+        <v>113.55</v>
+      </c>
+      <c r="H198" s="1">
+        <v>113.55</v>
+      </c>
+      <c r="I198" s="1">
+        <v>112.69</v>
+      </c>
+      <c r="J198" s="1">
+        <v>112.69</v>
+      </c>
+      <c r="K198" s="1">
+        <v>113.55</v>
+      </c>
+      <c r="L198" s="1">
+        <v>113.55</v>
+      </c>
+      <c r="M198" s="1">
+        <v>113.58</v>
+      </c>
+      <c r="N198" s="1">
+        <v>113.55</v>
+      </c>
+      <c r="O198" s="1">
+        <v>113.58</v>
+      </c>
+      <c r="P198" s="1">
+        <v>129.58000000000001</v>
+      </c>
+      <c r="Q198" s="1">
+        <v>129.58000000000001</v>
+      </c>
+      <c r="R198" s="1">
+        <v>129.58000000000001</v>
+      </c>
+      <c r="S198" s="1">
+        <v>129.58000000000001</v>
+      </c>
+      <c r="T198" s="1">
+        <v>191.58</v>
+      </c>
+      <c r="U198" s="1">
+        <v>359.58</v>
+      </c>
+      <c r="V198" s="1">
+        <v>129.58000000000001</v>
+      </c>
+      <c r="W198" s="1">
+        <v>129.58000000000001</v>
+      </c>
+      <c r="X198" s="1">
+        <v>129.58000000000001</v>
+      </c>
+      <c r="Y198" s="1">
+        <v>113.55</v>
+      </c>
+      <c r="Z198" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A199" s="3">
+        <v>45855</v>
+      </c>
+      <c r="B199" s="1">
+        <v>105.04</v>
+      </c>
+      <c r="C199" s="1">
+        <v>105.04</v>
+      </c>
+      <c r="D199" s="1">
+        <v>105.04</v>
+      </c>
+      <c r="E199" s="1">
+        <v>105.04</v>
+      </c>
+      <c r="F199" s="1">
+        <v>105.04</v>
+      </c>
+      <c r="G199" s="1">
+        <v>105.04</v>
+      </c>
+      <c r="H199" s="1">
+        <v>105.04</v>
+      </c>
+      <c r="I199" s="1">
+        <v>105.04</v>
+      </c>
+      <c r="J199" s="1">
+        <v>108.07</v>
+      </c>
+      <c r="K199" s="1">
+        <v>110.87</v>
+      </c>
+      <c r="L199" s="1">
+        <v>110.87</v>
+      </c>
+      <c r="M199" s="1">
+        <v>111.57</v>
+      </c>
+      <c r="N199" s="1">
+        <v>110.87</v>
+      </c>
+      <c r="O199" s="1">
+        <v>110.87</v>
+      </c>
+      <c r="P199" s="1">
+        <v>111.57</v>
+      </c>
+      <c r="Q199" s="1">
+        <v>112.53</v>
+      </c>
+      <c r="R199" s="1">
+        <v>112.57</v>
+      </c>
+      <c r="S199" s="1">
+        <v>112.53</v>
+      </c>
+      <c r="T199" s="1">
+        <v>112.57</v>
+      </c>
+      <c r="U199" s="1">
+        <v>308.57</v>
+      </c>
+      <c r="V199" s="1">
+        <v>190.57</v>
+      </c>
+      <c r="W199" s="1">
+        <v>112.57</v>
+      </c>
+      <c r="X199" s="1">
+        <v>112.53</v>
+      </c>
+      <c r="Y199" s="1">
+        <v>111.57</v>
+      </c>
+      <c r="Z199" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A200" s="3">
+        <v>45856</v>
+      </c>
+      <c r="B200" s="1">
+        <v>105.1</v>
+      </c>
+      <c r="C200" s="1">
+        <v>105.1</v>
+      </c>
+      <c r="D200" s="1">
+        <v>105.1</v>
+      </c>
+      <c r="E200" s="1">
+        <v>105.1</v>
+      </c>
+      <c r="F200" s="1">
+        <v>105.1</v>
+      </c>
+      <c r="G200" s="1">
+        <v>108.13</v>
+      </c>
+      <c r="H200" s="1">
+        <v>108.13</v>
+      </c>
+      <c r="I200" s="1">
+        <v>105.1</v>
+      </c>
+      <c r="J200" s="1">
+        <v>105.1</v>
+      </c>
+      <c r="K200" s="1">
+        <v>105.1</v>
+      </c>
+      <c r="L200" s="1">
+        <v>110.63</v>
+      </c>
+      <c r="M200" s="1">
+        <v>110.63</v>
+      </c>
+      <c r="N200" s="1">
+        <v>110.63</v>
+      </c>
+      <c r="O200" s="1">
+        <v>110.63</v>
+      </c>
+      <c r="P200" s="1">
+        <v>111.74</v>
+      </c>
+      <c r="Q200" s="1">
+        <v>111.74</v>
+      </c>
+      <c r="R200" s="1">
+        <v>112.59</v>
+      </c>
+      <c r="S200" s="1">
+        <v>112.59</v>
+      </c>
+      <c r="T200" s="1">
+        <v>190.63</v>
+      </c>
+      <c r="U200" s="1">
+        <v>830.59</v>
+      </c>
+      <c r="V200" s="1">
+        <v>112.73</v>
+      </c>
+      <c r="W200" s="1">
+        <v>112.59</v>
+      </c>
+      <c r="X200" s="1">
+        <v>111.74</v>
+      </c>
+      <c r="Y200" s="1">
+        <v>111.74</v>
+      </c>
+      <c r="Z200" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A201" s="3">
+        <v>45857</v>
+      </c>
+      <c r="B201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="C201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="D201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="E201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="F201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="G201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="H201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="I201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="J201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="K201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="L201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="M201" s="1">
+        <v>110.23</v>
+      </c>
+      <c r="N201" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="O201" s="1">
+        <v>110.23</v>
+      </c>
+      <c r="P201" s="1">
+        <v>111.9</v>
+      </c>
+      <c r="Q201" s="1">
+        <v>111.9</v>
+      </c>
+      <c r="R201" s="1">
+        <v>112.93</v>
+      </c>
+      <c r="S201" s="1">
+        <v>117.93</v>
+      </c>
+      <c r="T201" s="1">
+        <v>126.93</v>
+      </c>
+      <c r="U201" s="1">
+        <v>126.93</v>
+      </c>
+      <c r="V201" s="1">
+        <v>117.93</v>
+      </c>
+      <c r="W201" s="1">
+        <v>117.93</v>
+      </c>
+      <c r="X201" s="1">
+        <v>111.9</v>
+      </c>
+      <c r="Y201" s="1">
+        <v>110.83</v>
+      </c>
+      <c r="Z201" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A202" s="3">
+        <v>45858</v>
+      </c>
+      <c r="B202" s="1">
+        <v>110.38</v>
+      </c>
+      <c r="C202" s="1">
+        <v>110.38</v>
+      </c>
+      <c r="D202" s="1">
+        <v>110.38</v>
+      </c>
+      <c r="E202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="F202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="G202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="H202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="I202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="J202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="K202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="L202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="M202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="N202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="O202" s="1">
+        <v>105.35</v>
+      </c>
+      <c r="P202" s="1">
+        <v>110.38</v>
+      </c>
+      <c r="Q202" s="1">
+        <v>110.85</v>
+      </c>
+      <c r="R202" s="1">
+        <v>110.85</v>
+      </c>
+      <c r="S202" s="1">
+        <v>118.38</v>
+      </c>
+      <c r="T202" s="1">
+        <v>118.38</v>
+      </c>
+      <c r="U202" s="1">
+        <v>118.88</v>
+      </c>
+      <c r="V202" s="1">
+        <v>118.88</v>
+      </c>
+      <c r="W202" s="1">
+        <v>118.38</v>
+      </c>
+      <c r="X202" s="1">
+        <v>118.38</v>
+      </c>
+      <c r="Y202" s="1">
+        <v>118.38</v>
+      </c>
+      <c r="Z202" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="203" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A203" s="3">
+        <v>45859</v>
+      </c>
+      <c r="B203" s="1">
+        <v>104.88</v>
+      </c>
+      <c r="C203" s="1">
+        <v>104.88</v>
+      </c>
+      <c r="D203" s="1">
+        <v>104.88</v>
+      </c>
+      <c r="E203" s="1">
+        <v>104.88</v>
+      </c>
+      <c r="F203" s="1">
+        <v>104.88</v>
+      </c>
+      <c r="G203" s="1">
+        <v>109.89</v>
+      </c>
+      <c r="H203" s="1">
+        <v>109.89</v>
+      </c>
+      <c r="I203" s="1">
+        <v>109.89</v>
+      </c>
+      <c r="J203" s="1">
+        <v>109.91</v>
+      </c>
+      <c r="K203" s="1">
+        <v>109.91</v>
+      </c>
+      <c r="L203" s="1">
+        <v>110.38</v>
+      </c>
+      <c r="M203" s="1">
+        <v>110.38</v>
+      </c>
+      <c r="N203" s="1">
+        <v>110.38</v>
+      </c>
+      <c r="O203" s="1">
+        <v>111.36</v>
+      </c>
+      <c r="P203" s="1">
+        <v>118.41</v>
+      </c>
+      <c r="Q203" s="1">
+        <v>118.41</v>
+      </c>
+      <c r="R203" s="1">
+        <v>118.41</v>
+      </c>
+      <c r="S203" s="1">
+        <v>123.41</v>
+      </c>
+      <c r="T203" s="1">
+        <v>190.41</v>
+      </c>
+      <c r="U203" s="1">
+        <v>298.41000000000003</v>
+      </c>
+      <c r="V203" s="1">
+        <v>242.71</v>
+      </c>
+      <c r="W203" s="1">
+        <v>123.41</v>
+      </c>
+      <c r="X203" s="1">
+        <v>113.91</v>
+      </c>
+      <c r="Y203" s="1">
+        <v>111.36</v>
+      </c>
+      <c r="Z203" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="204" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A204" s="3">
+        <v>45860</v>
+      </c>
+      <c r="B204" s="1">
+        <v>113.06</v>
+      </c>
+      <c r="C204" s="1">
+        <v>113.06</v>
+      </c>
+      <c r="D204" s="1">
+        <v>113.06</v>
+      </c>
+      <c r="E204" s="1">
+        <v>113.06</v>
+      </c>
+      <c r="F204" s="1">
+        <v>113.06</v>
+      </c>
+      <c r="G204" s="1">
+        <v>120.11</v>
+      </c>
+      <c r="H204" s="1">
+        <v>120.11</v>
+      </c>
+      <c r="I204" s="1">
+        <v>120.11</v>
+      </c>
+      <c r="J204" s="1">
+        <v>121.11</v>
+      </c>
+      <c r="K204" s="1">
+        <v>121.11</v>
+      </c>
+      <c r="L204" s="1">
+        <v>121.11</v>
+      </c>
+      <c r="M204" s="1">
+        <v>121.11</v>
+      </c>
+      <c r="N204" s="1">
+        <v>121.11</v>
+      </c>
+      <c r="O204" s="1">
+        <v>129.11000000000001</v>
+      </c>
+      <c r="P204" s="1">
+        <v>129.11000000000001</v>
+      </c>
+      <c r="Q204" s="1">
+        <v>129.11000000000001</v>
+      </c>
+      <c r="R204" s="1">
+        <v>129.11000000000001</v>
+      </c>
+      <c r="S204" s="1">
+        <v>129.11000000000001</v>
+      </c>
+      <c r="T204" s="1">
+        <v>192.11</v>
+      </c>
+      <c r="U204" s="1">
+        <v>825.97</v>
+      </c>
+      <c r="V204" s="1">
+        <v>300.11</v>
+      </c>
+      <c r="W204" s="1">
+        <v>129.11000000000001</v>
+      </c>
+      <c r="X204" s="1">
+        <v>129.11000000000001</v>
+      </c>
+      <c r="Y204" s="1">
+        <v>121.11</v>
+      </c>
+      <c r="Z204" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="205" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A205" s="3">
+        <v>45861</v>
+      </c>
+      <c r="B205" s="1">
+        <v>113.65</v>
+      </c>
+      <c r="C205" s="1">
+        <v>113.65</v>
+      </c>
+      <c r="D205" s="1">
+        <v>113.65</v>
+      </c>
+      <c r="E205" s="1">
+        <v>113.65</v>
+      </c>
+      <c r="F205" s="1">
+        <v>113.65</v>
+      </c>
+      <c r="G205" s="1">
+        <v>119.69</v>
+      </c>
+      <c r="H205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="I205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="J205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="K205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="L205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="M205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="N205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="O205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="P205" s="1">
+        <v>121.69</v>
+      </c>
+      <c r="Q205" s="1">
+        <v>151.69</v>
+      </c>
+      <c r="R205" s="1">
+        <v>193.69</v>
+      </c>
+      <c r="S205" s="1">
+        <v>151.69</v>
+      </c>
+      <c r="T205" s="1">
+        <v>193.69</v>
+      </c>
+      <c r="U205" s="1">
+        <v>1047.9000000000001</v>
+      </c>
+      <c r="V205" s="1">
+        <v>151.69</v>
+      </c>
+      <c r="W205" s="1">
+        <v>121.69</v>
+      </c>
+      <c r="X205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="Y205" s="1">
+        <v>120.69</v>
+      </c>
+      <c r="Z205" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="206" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A206" s="3">
+        <v>45862</v>
+      </c>
+      <c r="B206" s="1">
+        <v>111.95</v>
+      </c>
+      <c r="C206" s="1">
+        <v>111.95</v>
+      </c>
+      <c r="D206" s="1">
+        <v>111.95</v>
+      </c>
+      <c r="E206" s="1">
+        <v>111.95</v>
+      </c>
+      <c r="F206" s="1">
+        <v>112.27</v>
+      </c>
+      <c r="G206" s="1">
+        <v>112.43</v>
+      </c>
+      <c r="H206" s="1">
+        <v>112.43</v>
+      </c>
+      <c r="I206" s="1">
+        <v>112.43</v>
+      </c>
+      <c r="J206" s="1">
+        <v>112.43</v>
+      </c>
+      <c r="K206" s="1">
+        <v>112.43</v>
+      </c>
+      <c r="L206" s="1">
+        <v>112.43</v>
+      </c>
+      <c r="M206" s="1">
+        <v>117.47</v>
+      </c>
+      <c r="N206" s="1">
+        <v>117.47</v>
+      </c>
+      <c r="O206" s="1">
+        <v>120.47</v>
+      </c>
+      <c r="P206" s="1">
+        <v>121.47</v>
+      </c>
+      <c r="Q206" s="1">
+        <v>192.47</v>
+      </c>
+      <c r="R206" s="1">
+        <v>192.47</v>
+      </c>
+      <c r="S206" s="1">
+        <v>150.47</v>
+      </c>
+      <c r="T206" s="1">
+        <v>192.47</v>
+      </c>
+      <c r="U206" s="1">
+        <v>826.32</v>
+      </c>
+      <c r="V206" s="1">
+        <v>295.47000000000003</v>
+      </c>
+      <c r="W206" s="1">
+        <v>192.47</v>
+      </c>
+      <c r="X206" s="1">
+        <v>121.47</v>
+      </c>
+      <c r="Y206" s="1">
+        <v>120.47</v>
+      </c>
+      <c r="Z206" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="207" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A207" s="3">
+        <v>45863</v>
+      </c>
+      <c r="B207" s="1">
+        <v>113.62</v>
+      </c>
+      <c r="C207" s="1">
+        <v>113.51</v>
+      </c>
+      <c r="D207" s="1">
+        <v>113.51</v>
+      </c>
+      <c r="E207" s="1">
+        <v>113.14</v>
+      </c>
+      <c r="F207" s="1">
+        <v>113.51</v>
+      </c>
+      <c r="G207" s="1">
+        <v>113.62</v>
+      </c>
+      <c r="H207" s="1">
+        <v>113.62</v>
+      </c>
+      <c r="I207" s="1">
+        <v>113.62</v>
+      </c>
+      <c r="J207" s="1">
+        <v>113.62</v>
+      </c>
+      <c r="K207" s="1">
+        <v>113.62</v>
+      </c>
+      <c r="L207" s="1">
+        <v>115.49</v>
+      </c>
+      <c r="M207" s="1">
+        <v>120.66</v>
+      </c>
+      <c r="N207" s="1">
+        <v>120.66</v>
+      </c>
+      <c r="O207" s="1">
+        <v>121.66</v>
+      </c>
+      <c r="P207" s="1">
+        <v>121.66</v>
+      </c>
+      <c r="Q207" s="1">
+        <v>122.66</v>
+      </c>
+      <c r="R207" s="1">
+        <v>122.66</v>
+      </c>
+      <c r="S207" s="1">
+        <v>122.66</v>
+      </c>
+      <c r="T207" s="1">
+        <v>193.66</v>
+      </c>
+      <c r="U207" s="1">
+        <v>296.66000000000003</v>
+      </c>
+      <c r="V207" s="1">
+        <v>151.66</v>
+      </c>
+      <c r="W207" s="1">
+        <v>122.66</v>
+      </c>
+      <c r="X207" s="1">
+        <v>121.66</v>
+      </c>
+      <c r="Y207" s="1">
+        <v>120.66</v>
+      </c>
+      <c r="Z207" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="208" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A208" s="3">
+        <v>45864</v>
+      </c>
+      <c r="B208" s="1">
+        <v>119.26</v>
+      </c>
+      <c r="C208" s="1">
+        <v>119.26</v>
+      </c>
+      <c r="D208" s="1">
+        <v>119.26</v>
+      </c>
+      <c r="E208" s="1">
+        <v>118.89</v>
+      </c>
+      <c r="F208" s="1">
+        <v>113.88</v>
+      </c>
+      <c r="G208" s="1">
+        <v>113.88</v>
+      </c>
+      <c r="H208" s="1">
+        <v>113.88</v>
+      </c>
+      <c r="I208" s="1">
+        <v>118.89</v>
+      </c>
+      <c r="J208" s="1">
+        <v>119.26</v>
+      </c>
+      <c r="K208" s="1">
+        <v>119.26</v>
+      </c>
+      <c r="L208" s="1">
+        <v>119.37</v>
+      </c>
+      <c r="M208" s="1">
+        <v>119.37</v>
+      </c>
+      <c r="N208" s="1">
+        <v>119.37</v>
+      </c>
+      <c r="O208" s="1">
+        <v>119.37</v>
+      </c>
+      <c r="P208" s="1">
+        <v>119.37</v>
+      </c>
+      <c r="Q208" s="1">
+        <v>120.52</v>
+      </c>
+      <c r="R208" s="1">
+        <v>128.41</v>
+      </c>
+      <c r="S208" s="1">
+        <v>128.41</v>
+      </c>
+      <c r="T208" s="1">
+        <v>129.41</v>
+      </c>
+      <c r="U208" s="1">
+        <v>157.41</v>
+      </c>
+      <c r="V208" s="1">
+        <v>129.41</v>
+      </c>
+      <c r="W208" s="1">
+        <v>128.41</v>
+      </c>
+      <c r="X208" s="1">
+        <v>121.61</v>
+      </c>
+      <c r="Y208" s="1">
+        <v>120.52</v>
+      </c>
+      <c r="Z208" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="209" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A209" s="3">
+        <v>45865</v>
+      </c>
+      <c r="B209" s="1">
+        <v>108.69</v>
+      </c>
+      <c r="C209" s="1">
+        <v>108.69</v>
+      </c>
+      <c r="D209" s="1">
+        <v>108.69</v>
+      </c>
+      <c r="E209" s="1">
+        <v>108.69</v>
+      </c>
+      <c r="F209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="G209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="H209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="I209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="J209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="K209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="L209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="M209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="N209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="O209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="P209" s="1">
+        <v>103.68</v>
+      </c>
+      <c r="Q209" s="1">
+        <v>108.69</v>
+      </c>
+      <c r="R209" s="1">
+        <v>109.18</v>
+      </c>
+      <c r="S209" s="1">
+        <v>112.34</v>
+      </c>
+      <c r="T209" s="1">
+        <v>116.71</v>
+      </c>
+      <c r="U209" s="1">
+        <v>118.21</v>
+      </c>
+      <c r="V209" s="1">
+        <v>118.21</v>
+      </c>
+      <c r="W209" s="1">
+        <v>116.71</v>
+      </c>
+      <c r="X209" s="1">
+        <v>116.71</v>
+      </c>
+      <c r="Y209" s="1">
+        <v>116.71</v>
+      </c>
+      <c r="Z209" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="210" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A210" s="3">
+        <v>45866</v>
+      </c>
+      <c r="B210" s="1">
+        <v>113.53</v>
+      </c>
+      <c r="C210" s="1">
+        <v>108.53</v>
+      </c>
+      <c r="D210" s="1">
+        <v>108.53</v>
+      </c>
+      <c r="E210" s="1">
+        <v>108.53</v>
+      </c>
+      <c r="F210" s="1">
+        <v>108.53</v>
+      </c>
+      <c r="G210" s="1">
+        <v>113.9</v>
+      </c>
+      <c r="H210" s="1">
+        <v>113.9</v>
+      </c>
+      <c r="I210" s="1">
+        <v>113.9</v>
+      </c>
+      <c r="J210" s="1">
+        <v>114.02</v>
+      </c>
+      <c r="K210" s="1">
+        <v>114.02</v>
+      </c>
+      <c r="L210" s="1">
+        <v>114.02</v>
+      </c>
+      <c r="M210" s="1">
+        <v>114.02</v>
+      </c>
+      <c r="N210" s="1">
+        <v>114.02</v>
+      </c>
+      <c r="O210" s="1">
+        <v>116.18</v>
+      </c>
+      <c r="P210" s="1">
+        <v>121.55</v>
+      </c>
+      <c r="Q210" s="1">
+        <v>121.55</v>
+      </c>
+      <c r="R210" s="1">
+        <v>122.05</v>
+      </c>
+      <c r="S210" s="1">
+        <v>122.05</v>
+      </c>
+      <c r="T210" s="1">
+        <v>194.05</v>
+      </c>
+      <c r="U210" s="1">
+        <v>827.91</v>
+      </c>
+      <c r="V210" s="1">
+        <v>122.05</v>
+      </c>
+      <c r="W210" s="1">
+        <v>122.05</v>
+      </c>
+      <c r="X210" s="1">
+        <v>121.55</v>
+      </c>
+      <c r="Y210" s="1">
+        <v>121.55</v>
+      </c>
+      <c r="Z210" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="211" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A211" s="3">
+        <v>45867</v>
+      </c>
+      <c r="B211" s="1">
+        <v>106.25</v>
+      </c>
+      <c r="C211" s="1">
+        <v>106.25</v>
+      </c>
+      <c r="D211" s="1">
+        <v>106.25</v>
+      </c>
+      <c r="E211" s="1">
+        <v>106.25</v>
+      </c>
+      <c r="F211" s="1">
+        <v>106.25</v>
+      </c>
+      <c r="G211" s="1">
+        <v>106.25</v>
+      </c>
+      <c r="H211" s="1">
+        <v>106.25</v>
+      </c>
+      <c r="I211" s="1">
+        <v>111.26</v>
+      </c>
+      <c r="J211" s="1">
+        <v>111.28</v>
+      </c>
+      <c r="K211" s="1">
+        <v>111.28</v>
+      </c>
+      <c r="L211" s="1">
+        <v>111.28</v>
+      </c>
+      <c r="M211" s="1">
+        <v>111.28</v>
+      </c>
+      <c r="N211" s="1">
+        <v>111.28</v>
+      </c>
+      <c r="O211" s="1">
+        <v>111.28</v>
+      </c>
+      <c r="P211" s="1">
+        <v>113.91</v>
+      </c>
+      <c r="Q211" s="1">
+        <v>191.78</v>
+      </c>
+      <c r="R211" s="1">
+        <v>191.78</v>
+      </c>
+      <c r="S211" s="1">
+        <v>133.78</v>
+      </c>
+      <c r="T211" s="1">
+        <v>191.78</v>
+      </c>
+      <c r="U211" s="1">
+        <v>294.77999999999997</v>
+      </c>
+      <c r="V211" s="1">
+        <v>191.78</v>
+      </c>
+      <c r="W211" s="1">
+        <v>116.78</v>
+      </c>
+      <c r="X211" s="1">
+        <v>111.28</v>
+      </c>
+      <c r="Y211" s="1">
+        <v>111.26</v>
+      </c>
+      <c r="Z211" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="212" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A212" s="3">
+        <v>45868</v>
+      </c>
+      <c r="B212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="C212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="D212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="E212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="F212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="G212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="H212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="I212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="J212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="K212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="L212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="M212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="N212" s="1">
+        <v>109.81</v>
+      </c>
+      <c r="O212" s="1">
+        <v>114.82</v>
+      </c>
+      <c r="P212" s="1">
+        <v>117.42</v>
+      </c>
+      <c r="Q212" s="1">
+        <v>132.34</v>
+      </c>
+      <c r="R212" s="1">
+        <v>195.34</v>
+      </c>
+      <c r="S212" s="1">
+        <v>132.34</v>
+      </c>
+      <c r="T212" s="1">
+        <v>195.34</v>
+      </c>
+      <c r="U212" s="1">
+        <v>829.19</v>
+      </c>
+      <c r="V212" s="1">
+        <v>829.19</v>
+      </c>
+      <c r="W212" s="1">
+        <v>132.34</v>
+      </c>
+      <c r="X212" s="1">
+        <v>114.84</v>
+      </c>
+      <c r="Y212" s="1">
+        <v>114.82</v>
+      </c>
+      <c r="Z212" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="213" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A213" s="3">
+        <v>45869</v>
+      </c>
+      <c r="B213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="C213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="D213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="E213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="F213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="G213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="H213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="I213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="J213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="K213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="L213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="M213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="N213" s="1">
+        <v>104.82</v>
+      </c>
+      <c r="O213" s="1">
+        <v>109.83</v>
+      </c>
+      <c r="P213" s="1">
+        <v>117.34</v>
+      </c>
+      <c r="Q213" s="1">
+        <v>158.34</v>
+      </c>
+      <c r="R213" s="1">
+        <v>190.34</v>
+      </c>
+      <c r="S213" s="1">
+        <v>158.34</v>
+      </c>
+      <c r="T213" s="1">
+        <v>190.34</v>
+      </c>
+      <c r="U213" s="1">
+        <v>824.2</v>
+      </c>
+      <c r="V213" s="1">
+        <v>824.2</v>
+      </c>
+      <c r="W213" s="1">
+        <v>158.34</v>
+      </c>
+      <c r="X213" s="1">
+        <v>117.34</v>
+      </c>
+      <c r="Y213" s="1">
+        <v>109.85</v>
+      </c>
+      <c r="Z213" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A182">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="notEqual">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:AA182">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="notEqual">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:XFD182 A214:XFD1048576">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A183:A213">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AA182">
+  <conditionalFormatting sqref="A183:AA213">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1048576">
+  <conditionalFormatting sqref="A183:XFD213">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
@@ -15148,15 +17703,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101002BA42287BCA96E4CBE0B0D4D30D58F77" ma:contentTypeVersion="1" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="430dbe27c8d3fdb5344da83a654157b0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e48ec5c2-614c-49e6-a81a-ca54d4b077b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="acf7ea99d1f8bcbadb4a28bdb40ccc60" ns2:_="">
     <xsd:import namespace="e48ec5c2-614c-49e6-a81a-ca54d4b077b0"/>
@@ -15296,6 +17842,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -15303,14 +17858,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{461BE8A5-4C25-4C42-96DB-D4C1C964625B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3959B7EB-E1F5-4E6B-B13B-1914B8532C51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15328,6 +17875,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{461BE8A5-4C25-4C42-96DB-D4C1C964625B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7832A24B-F3AA-41AB-A1B9-AF354BD81C2E}">
   <ds:schemaRefs>
